--- a/file/table/DAPC_ElectricElbowBellEnd.xlsx
+++ b/file/table/DAPC_ElectricElbowBellEnd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30593DF-3B7E-40FF-B858-95A9FD07D91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61129ED4-16F1-4268-8DCB-4541D3BC40E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D413FB54-6771-4A8E-8770-B93D70107D30}"/>
   </bookViews>
@@ -449,15 +449,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>439615</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>124258</xdr:rowOff>
+      <xdr:colOff>262759</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>539261</xdr:colOff>
+      <xdr:colOff>118847</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>119747</xdr:rowOff>
+      <xdr:rowOff>19898</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -492,8 +492,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6512169" y="546289"/>
-          <a:ext cx="3358661" cy="2949704"/>
+          <a:off x="6332483" y="673802"/>
+          <a:ext cx="3114295" cy="2793489"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/file/table/DAPC_ElectricElbowBellEnd.xlsx
+++ b/file/table/DAPC_ElectricElbowBellEnd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61129ED4-16F1-4268-8DCB-4541D3BC40E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E884C7A0-7683-4BDD-B3F8-460DFDEED6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D413FB54-6771-4A8E-8770-B93D70107D30}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="38">
   <si>
     <t>Item</t>
   </si>
@@ -141,6 +141,15 @@
   </si>
   <si>
     <t>External Wall offset (mm)</t>
+  </si>
+  <si>
+    <t>B' (mm) Min.</t>
+  </si>
+  <si>
+    <t>A' Sch40 (mm)</t>
+  </si>
+  <si>
+    <t>A' Sch80 (mm)</t>
   </si>
 </sst>
 </file>
@@ -176,7 +185,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -311,6 +320,32 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
       <top style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
@@ -323,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -379,6 +414,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,13 +441,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -449,22 +490,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>262759</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>27416</xdr:rowOff>
+      <xdr:colOff>111369</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>29306</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>118847</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>125509</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>19898</xdr:rowOff>
+      <xdr:rowOff>199293</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0D6B356-CF71-6998-A107-E105F7DB1671}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE8C3A7D-1C76-D99C-0911-3C7361AE9139}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -492,8 +533,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6332483" y="673802"/>
-          <a:ext cx="3114295" cy="2793489"/>
+          <a:off x="6183923" y="451337"/>
+          <a:ext cx="3596304" cy="3124202"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -822,13 +863,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03377F46-21A8-46AD-BDC5-1FB7BCB4429A}">
-  <dimension ref="B2:P34"/>
+  <dimension ref="B2:S34"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="11.88671875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="10.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="9.33203125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="11.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5546875" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9.88671875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.33203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
@@ -1168,7 +1221,7 @@
       <c r="I16" s="20"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
@@ -1193,19 +1246,19 @@
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="N19" s="19"/>
+      <c r="P19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19">
+      <c r="Q19" s="19">
         <v>25.4</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B20" s="4" t="s">
         <v>0</v>
       </c>
@@ -1233,16 +1286,25 @@
         <v>26</v>
       </c>
       <c r="L20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="M20" s="5" t="s">
+      <c r="O20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N20" s="6" t="s">
+      <c r="P20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q20" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -1263,9 +1325,12 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="9"/>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="9"/>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1277,7 +1342,7 @@
         <v>0.5</v>
       </c>
       <c r="E22" s="17">
-        <f>D22*$M$19</f>
+        <f>D22*$Q$19</f>
         <v>12.7</v>
       </c>
       <c r="F22" s="17">
@@ -1285,11 +1350,11 @@
         <v>6.35</v>
       </c>
       <c r="G22" s="13">
-        <f>D5*$M$19</f>
+        <f>D5*$Q$19</f>
         <v>2.7685999999999997</v>
       </c>
       <c r="H22" s="13">
-        <f>E5*$M$19</f>
+        <f>E5*$Q$19</f>
         <v>3.7337999999999996</v>
       </c>
       <c r="I22" s="13">
@@ -1301,27 +1366,35 @@
         <v>10.0838</v>
       </c>
       <c r="K22" s="13">
-        <f>F5*$M$19</f>
+        <f>F5*$Q$19</f>
         <v>21.335999999999999</v>
       </c>
       <c r="L22" s="13">
+        <f>$K22-2*G22</f>
+        <v>15.7988</v>
+      </c>
+      <c r="M22" s="13">
+        <f>$K22-2*H22</f>
+        <v>13.868399999999999</v>
+      </c>
+      <c r="N22" s="13">
         <f>K22/2</f>
         <v>10.667999999999999</v>
       </c>
-      <c r="M22" s="13">
-        <f>G5*$M$19</f>
+      <c r="O22" s="13">
+        <f>G5*$Q$19</f>
         <v>38.099999999999994</v>
       </c>
-      <c r="N22" s="14">
-        <f>H5*$M$19</f>
+      <c r="P22" s="21">
+        <f>O22*0.1</f>
+        <v>3.8099999999999996</v>
+      </c>
+      <c r="Q22" s="14">
+        <f>H5*$Q$19</f>
         <v>101.6</v>
       </c>
-      <c r="O22" s="1">
-        <f>E22+G22</f>
-        <v>15.468599999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
@@ -1333,7 +1406,7 @@
         <v>0.75</v>
       </c>
       <c r="E23" s="17">
-        <f>D23*$M$19</f>
+        <f>D23*$Q$19</f>
         <v>19.049999999999997</v>
       </c>
       <c r="F23" s="17">
@@ -1341,39 +1414,51 @@
         <v>9.5249999999999986</v>
       </c>
       <c r="G23" s="13">
-        <f t="shared" ref="G23:G34" si="1">D6*$M$19</f>
+        <f>D6*$Q$19</f>
         <v>2.8702000000000001</v>
       </c>
       <c r="H23" s="13">
-        <f t="shared" ref="H23:H34" si="2">E6*$M$19</f>
+        <f>E6*$Q$19</f>
         <v>3.9115999999999995</v>
       </c>
       <c r="I23" s="13">
-        <f t="shared" ref="I23:I34" si="3">$F23+G23</f>
+        <f t="shared" ref="I23:I34" si="1">$F23+G23</f>
         <v>12.395199999999999</v>
       </c>
       <c r="J23" s="13">
-        <f t="shared" ref="J23:J34" si="4">$F23+H23</f>
+        <f t="shared" ref="J23:J34" si="2">$F23+H23</f>
         <v>13.436599999999999</v>
       </c>
       <c r="K23" s="13">
-        <f t="shared" ref="K23:K34" si="5">F6*$M$19</f>
+        <f>F6*$Q$19</f>
         <v>26.669999999999998</v>
       </c>
       <c r="L23" s="13">
-        <f t="shared" ref="L23:L34" si="6">K23/2</f>
+        <f>K23-2*G23</f>
+        <v>20.929599999999997</v>
+      </c>
+      <c r="M23" s="13">
+        <f t="shared" ref="M23:M34" si="3">$K23-2*H23</f>
+        <v>18.846799999999998</v>
+      </c>
+      <c r="N23" s="13">
+        <f t="shared" ref="N23:N34" si="4">K23/2</f>
         <v>13.334999999999999</v>
       </c>
-      <c r="M23" s="13">
-        <f t="shared" ref="M23:M34" si="7">G6*$M$19</f>
+      <c r="O23" s="13">
+        <f>G6*$Q$19</f>
         <v>38.099999999999994</v>
       </c>
-      <c r="N23" s="14">
-        <f t="shared" ref="N23:N34" si="8">H6*$M$19</f>
+      <c r="P23" s="21">
+        <f t="shared" ref="P23:P34" si="5">O23*0.1</f>
+        <v>3.8099999999999996</v>
+      </c>
+      <c r="Q23" s="14">
+        <f>H6*$Q$19</f>
         <v>114.3</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
@@ -1384,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="17">
-        <f>D24*$M$19</f>
+        <f>D24*$Q$19</f>
         <v>25.4</v>
       </c>
       <c r="F24" s="17">
@@ -1392,39 +1477,51 @@
         <v>12.7</v>
       </c>
       <c r="G24" s="13">
+        <f>D7*$Q$19</f>
+        <v>3.3782000000000001</v>
+      </c>
+      <c r="H24" s="13">
+        <f>E7*$Q$19</f>
+        <v>4.5465999999999998</v>
+      </c>
+      <c r="I24" s="13">
         <f t="shared" si="1"/>
-        <v>3.3782000000000001</v>
-      </c>
-      <c r="H24" s="13">
+        <v>16.078199999999999</v>
+      </c>
+      <c r="J24" s="13">
         <f t="shared" si="2"/>
-        <v>4.5465999999999998</v>
-      </c>
-      <c r="I24" s="13">
+        <v>17.246600000000001</v>
+      </c>
+      <c r="K24" s="13">
+        <f>F7*$Q$19</f>
+        <v>33.400999999999996</v>
+      </c>
+      <c r="L24" s="13">
+        <f>K24-2*G24</f>
+        <v>26.644599999999997</v>
+      </c>
+      <c r="M24" s="13">
         <f t="shared" si="3"/>
-        <v>16.078199999999999</v>
-      </c>
-      <c r="J24" s="13">
+        <v>24.307799999999997</v>
+      </c>
+      <c r="N24" s="13">
         <f t="shared" si="4"/>
-        <v>17.246600000000001</v>
-      </c>
-      <c r="K24" s="13">
+        <v>16.700499999999998</v>
+      </c>
+      <c r="O24" s="13">
+        <f>G7*$Q$19</f>
+        <v>47.625</v>
+      </c>
+      <c r="P24" s="21">
         <f t="shared" si="5"/>
-        <v>33.400999999999996</v>
-      </c>
-      <c r="L24" s="13">
-        <f t="shared" si="6"/>
-        <v>16.700499999999998</v>
-      </c>
-      <c r="M24" s="13">
-        <f t="shared" si="7"/>
-        <v>47.625</v>
-      </c>
-      <c r="N24" s="14">
-        <f t="shared" si="8"/>
+        <v>4.7625000000000002</v>
+      </c>
+      <c r="Q24" s="14">
+        <f>H7*$Q$19</f>
         <v>146.04999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
@@ -1436,7 +1533,7 @@
         <v>1.25</v>
       </c>
       <c r="E25" s="17">
-        <f>D25*$M$19</f>
+        <f>D25*$Q$19</f>
         <v>31.75</v>
       </c>
       <c r="F25" s="17">
@@ -1444,39 +1541,51 @@
         <v>15.875</v>
       </c>
       <c r="G25" s="13">
+        <f>D8*$Q$19</f>
+        <v>3.556</v>
+      </c>
+      <c r="H25" s="13">
+        <f>E8*$Q$19</f>
+        <v>4.8513999999999999</v>
+      </c>
+      <c r="I25" s="13">
         <f t="shared" si="1"/>
-        <v>3.556</v>
-      </c>
-      <c r="H25" s="13">
+        <v>19.431000000000001</v>
+      </c>
+      <c r="J25" s="13">
         <f t="shared" si="2"/>
-        <v>4.8513999999999999</v>
-      </c>
-      <c r="I25" s="13">
+        <v>20.726399999999998</v>
+      </c>
+      <c r="K25" s="13">
+        <f>F8*$Q$19</f>
+        <v>42.163999999999994</v>
+      </c>
+      <c r="L25" s="13">
+        <f>K25-2*G25</f>
+        <v>35.051999999999992</v>
+      </c>
+      <c r="M25" s="13">
         <f t="shared" si="3"/>
-        <v>19.431000000000001</v>
-      </c>
-      <c r="J25" s="13">
+        <v>32.461199999999991</v>
+      </c>
+      <c r="N25" s="13">
         <f t="shared" si="4"/>
-        <v>20.726399999999998</v>
-      </c>
-      <c r="K25" s="13">
+        <v>21.081999999999997</v>
+      </c>
+      <c r="O25" s="13">
+        <f>G8*$Q$19</f>
+        <v>50.8</v>
+      </c>
+      <c r="P25" s="21">
         <f t="shared" si="5"/>
-        <v>42.163999999999994</v>
-      </c>
-      <c r="L25" s="13">
-        <f t="shared" si="6"/>
-        <v>21.081999999999997</v>
-      </c>
-      <c r="M25" s="13">
-        <f t="shared" si="7"/>
-        <v>50.8</v>
-      </c>
-      <c r="N25" s="14">
-        <f t="shared" si="8"/>
+        <v>5.08</v>
+      </c>
+      <c r="Q25" s="14">
+        <f>H8*$Q$19</f>
         <v>184.14999999999998</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
@@ -1488,7 +1597,7 @@
         <v>1.5</v>
       </c>
       <c r="E26" s="17">
-        <f>D26*$M$19</f>
+        <f>D26*$Q$19</f>
         <v>38.099999999999994</v>
       </c>
       <c r="F26" s="17">
@@ -1496,39 +1605,51 @@
         <v>19.049999999999997</v>
       </c>
       <c r="G26" s="13">
+        <f>D9*$Q$19</f>
+        <v>3.6829999999999994</v>
+      </c>
+      <c r="H26" s="13">
+        <f>E9*$Q$19</f>
+        <v>5.08</v>
+      </c>
+      <c r="I26" s="13">
         <f t="shared" si="1"/>
-        <v>3.6829999999999994</v>
-      </c>
-      <c r="H26" s="13">
+        <v>22.732999999999997</v>
+      </c>
+      <c r="J26" s="13">
         <f t="shared" si="2"/>
+        <v>24.129999999999995</v>
+      </c>
+      <c r="K26" s="13">
+        <f>F9*$Q$19</f>
+        <v>48.26</v>
+      </c>
+      <c r="L26" s="13">
+        <f t="shared" ref="L26:L34" si="6">K26-2*G26</f>
+        <v>40.893999999999998</v>
+      </c>
+      <c r="M26" s="13">
+        <f t="shared" si="3"/>
+        <v>38.099999999999994</v>
+      </c>
+      <c r="N26" s="13">
+        <f t="shared" si="4"/>
+        <v>24.13</v>
+      </c>
+      <c r="O26" s="13">
+        <f>G9*$Q$19</f>
+        <v>50.8</v>
+      </c>
+      <c r="P26" s="21">
+        <f t="shared" si="5"/>
         <v>5.08</v>
       </c>
-      <c r="I26" s="13">
-        <f t="shared" si="3"/>
-        <v>22.732999999999997</v>
-      </c>
-      <c r="J26" s="13">
-        <f t="shared" si="4"/>
-        <v>24.129999999999995</v>
-      </c>
-      <c r="K26" s="13">
-        <f t="shared" si="5"/>
-        <v>48.26</v>
-      </c>
-      <c r="L26" s="13">
-        <f t="shared" si="6"/>
-        <v>24.13</v>
-      </c>
-      <c r="M26" s="13">
-        <f t="shared" si="7"/>
-        <v>50.8</v>
-      </c>
-      <c r="N26" s="14">
-        <f t="shared" si="8"/>
+      <c r="Q26" s="14">
+        <f>H9*$Q$19</f>
         <v>209.54999999999998</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B27" s="2" t="s">
         <v>18</v>
       </c>
@@ -1539,7 +1660,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="17">
-        <f>D27*$M$19</f>
+        <f>D27*$Q$19</f>
         <v>50.8</v>
       </c>
       <c r="F27" s="17">
@@ -1547,39 +1668,51 @@
         <v>25.4</v>
       </c>
       <c r="G27" s="13">
+        <f>D10*$Q$19</f>
+        <v>3.9115999999999995</v>
+      </c>
+      <c r="H27" s="13">
+        <f>E10*$Q$19</f>
+        <v>5.5371999999999995</v>
+      </c>
+      <c r="I27" s="13">
         <f t="shared" si="1"/>
-        <v>3.9115999999999995</v>
-      </c>
-      <c r="H27" s="13">
+        <v>29.311599999999999</v>
+      </c>
+      <c r="J27" s="13">
         <f t="shared" si="2"/>
-        <v>5.5371999999999995</v>
-      </c>
-      <c r="I27" s="13">
-        <f t="shared" si="3"/>
-        <v>29.311599999999999</v>
-      </c>
-      <c r="J27" s="13">
-        <f t="shared" si="4"/>
         <v>30.937199999999997</v>
       </c>
       <c r="K27" s="13">
-        <f t="shared" si="5"/>
+        <f>F10*$Q$19</f>
         <v>60.324999999999996</v>
       </c>
       <c r="L27" s="13">
         <f t="shared" si="6"/>
+        <v>52.501799999999996</v>
+      </c>
+      <c r="M27" s="13">
+        <f t="shared" si="3"/>
+        <v>49.250599999999999</v>
+      </c>
+      <c r="N27" s="13">
+        <f t="shared" si="4"/>
         <v>30.162499999999998</v>
       </c>
-      <c r="M27" s="13">
-        <f t="shared" si="7"/>
+      <c r="O27" s="13">
+        <f>G10*$Q$19</f>
         <v>50.8</v>
       </c>
-      <c r="N27" s="14">
-        <f t="shared" si="8"/>
+      <c r="P27" s="21">
+        <f t="shared" si="5"/>
+        <v>5.08</v>
+      </c>
+      <c r="Q27" s="14">
+        <f>H10*$Q$19</f>
         <v>241.29999999999998</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B28" s="2" t="s">
         <v>17</v>
       </c>
@@ -1591,7 +1724,7 @@
         <v>2.5</v>
       </c>
       <c r="E28" s="17">
-        <f>D28*$M$19</f>
+        <f>D28*$Q$19</f>
         <v>63.5</v>
       </c>
       <c r="F28" s="17">
@@ -1599,39 +1732,51 @@
         <v>31.75</v>
       </c>
       <c r="G28" s="13">
+        <f>D11*$Q$19</f>
+        <v>5.1562000000000001</v>
+      </c>
+      <c r="H28" s="13">
+        <f>E11*$Q$19</f>
+        <v>7.0104000000000006</v>
+      </c>
+      <c r="I28" s="13">
         <f t="shared" si="1"/>
-        <v>5.1562000000000001</v>
-      </c>
-      <c r="H28" s="13">
+        <v>36.906199999999998</v>
+      </c>
+      <c r="J28" s="13">
         <f t="shared" si="2"/>
-        <v>7.0104000000000006</v>
-      </c>
-      <c r="I28" s="13">
-        <f t="shared" si="3"/>
-        <v>36.906199999999998</v>
-      </c>
-      <c r="J28" s="13">
-        <f t="shared" si="4"/>
         <v>38.760400000000004</v>
       </c>
       <c r="K28" s="13">
-        <f t="shared" si="5"/>
+        <f>F11*$Q$19</f>
         <v>73.024999999999991</v>
       </c>
       <c r="L28" s="13">
         <f t="shared" si="6"/>
+        <v>62.712599999999995</v>
+      </c>
+      <c r="M28" s="13">
+        <f t="shared" si="3"/>
+        <v>59.00419999999999</v>
+      </c>
+      <c r="N28" s="13">
+        <f t="shared" si="4"/>
         <v>36.512499999999996</v>
       </c>
-      <c r="M28" s="13">
-        <f t="shared" si="7"/>
+      <c r="O28" s="13">
+        <f>G11*$Q$19</f>
         <v>76.199999999999989</v>
       </c>
-      <c r="N28" s="14">
-        <f t="shared" si="8"/>
+      <c r="P28" s="21">
+        <f t="shared" si="5"/>
+        <v>7.6199999999999992</v>
+      </c>
+      <c r="Q28" s="14">
+        <f>H11*$Q$19</f>
         <v>266.7</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B29" s="2" t="s">
         <v>18</v>
       </c>
@@ -1642,7 +1787,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="17">
-        <f>D29*$M$19</f>
+        <f>D29*$Q$19</f>
         <v>76.199999999999989</v>
       </c>
       <c r="F29" s="17">
@@ -1650,39 +1795,51 @@
         <v>38.099999999999994</v>
       </c>
       <c r="G29" s="13">
+        <f>D12*$Q$19</f>
+        <v>5.4863999999999997</v>
+      </c>
+      <c r="H29" s="13">
+        <f>E12*$Q$19</f>
+        <v>7.6199999999999992</v>
+      </c>
+      <c r="I29" s="13">
         <f t="shared" si="1"/>
-        <v>5.4863999999999997</v>
-      </c>
-      <c r="H29" s="13">
+        <v>43.586399999999998</v>
+      </c>
+      <c r="J29" s="13">
         <f t="shared" si="2"/>
-        <v>7.6199999999999992</v>
-      </c>
-      <c r="I29" s="13">
-        <f t="shared" si="3"/>
-        <v>43.586399999999998</v>
-      </c>
-      <c r="J29" s="13">
-        <f t="shared" si="4"/>
         <v>45.719999999999992</v>
       </c>
       <c r="K29" s="13">
-        <f t="shared" si="5"/>
+        <f>F12*$Q$19</f>
         <v>88.899999999999991</v>
       </c>
       <c r="L29" s="13">
         <f t="shared" si="6"/>
+        <v>77.927199999999999</v>
+      </c>
+      <c r="M29" s="13">
+        <f t="shared" si="3"/>
+        <v>73.66</v>
+      </c>
+      <c r="N29" s="13">
+        <f t="shared" si="4"/>
         <v>44.449999999999996</v>
       </c>
-      <c r="M29" s="13">
-        <f t="shared" si="7"/>
+      <c r="O29" s="13">
+        <f>G12*$Q$19</f>
         <v>79.375</v>
       </c>
-      <c r="N29" s="14">
-        <f t="shared" si="8"/>
+      <c r="P29" s="21">
+        <f t="shared" si="5"/>
+        <v>7.9375</v>
+      </c>
+      <c r="Q29" s="14">
+        <f>H12*$Q$19</f>
         <v>330.2</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B30" s="2" t="s">
         <v>17</v>
       </c>
@@ -1694,7 +1851,7 @@
         <v>3.5</v>
       </c>
       <c r="E30" s="17">
-        <f>D30*$M$19</f>
+        <f>D30*$Q$19</f>
         <v>88.899999999999991</v>
       </c>
       <c r="F30" s="17">
@@ -1702,39 +1859,51 @@
         <v>44.449999999999996</v>
       </c>
       <c r="G30" s="13">
+        <f>D13*$Q$19</f>
+        <v>5.7404000000000002</v>
+      </c>
+      <c r="H30" s="13">
+        <f>E13*$Q$19</f>
+        <v>8.0771999999999995</v>
+      </c>
+      <c r="I30" s="13">
         <f t="shared" si="1"/>
-        <v>5.7404000000000002</v>
-      </c>
-      <c r="H30" s="13">
+        <v>50.190399999999997</v>
+      </c>
+      <c r="J30" s="13">
         <f t="shared" si="2"/>
-        <v>8.0771999999999995</v>
-      </c>
-      <c r="I30" s="13">
-        <f t="shared" si="3"/>
-        <v>50.190399999999997</v>
-      </c>
-      <c r="J30" s="13">
-        <f t="shared" si="4"/>
         <v>52.527199999999993</v>
       </c>
       <c r="K30" s="13">
-        <f t="shared" si="5"/>
+        <f>F13*$Q$19</f>
         <v>101.6</v>
       </c>
       <c r="L30" s="13">
         <f t="shared" si="6"/>
+        <v>90.119199999999992</v>
+      </c>
+      <c r="M30" s="13">
+        <f t="shared" si="3"/>
+        <v>85.445599999999999</v>
+      </c>
+      <c r="N30" s="13">
+        <f t="shared" si="4"/>
         <v>50.8</v>
       </c>
-      <c r="M30" s="13">
-        <f t="shared" si="7"/>
+      <c r="O30" s="13">
+        <f>G13*$Q$19</f>
         <v>82.55</v>
       </c>
-      <c r="N30" s="14">
-        <f t="shared" si="8"/>
+      <c r="P30" s="21">
+        <f t="shared" si="5"/>
+        <v>8.2550000000000008</v>
+      </c>
+      <c r="Q30" s="14">
+        <f>H13*$Q$19</f>
         <v>381</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B31" s="2" t="s">
         <v>18</v>
       </c>
@@ -1745,7 +1914,7 @@
         <v>4</v>
       </c>
       <c r="E31" s="17">
-        <f>D31*$M$19</f>
+        <f>D31*$Q$19</f>
         <v>101.6</v>
       </c>
       <c r="F31" s="17">
@@ -1753,39 +1922,51 @@
         <v>50.8</v>
       </c>
       <c r="G31" s="13">
+        <f>D14*$Q$19</f>
+        <v>6.0197999999999992</v>
+      </c>
+      <c r="H31" s="13">
+        <f>E14*$Q$19</f>
+        <v>8.5597999999999992</v>
+      </c>
+      <c r="I31" s="13">
         <f t="shared" si="1"/>
-        <v>6.0197999999999992</v>
-      </c>
-      <c r="H31" s="13">
+        <v>56.819799999999994</v>
+      </c>
+      <c r="J31" s="13">
         <f t="shared" si="2"/>
-        <v>8.5597999999999992</v>
-      </c>
-      <c r="I31" s="13">
-        <f t="shared" si="3"/>
-        <v>56.819799999999994</v>
-      </c>
-      <c r="J31" s="13">
-        <f t="shared" si="4"/>
         <v>59.359799999999993</v>
       </c>
       <c r="K31" s="13">
-        <f t="shared" si="5"/>
+        <f>F14*$Q$19</f>
         <v>114.3</v>
       </c>
       <c r="L31" s="13">
         <f t="shared" si="6"/>
+        <v>102.2604</v>
+      </c>
+      <c r="M31" s="13">
+        <f t="shared" si="3"/>
+        <v>97.180399999999992</v>
+      </c>
+      <c r="N31" s="13">
+        <f t="shared" si="4"/>
         <v>57.15</v>
       </c>
-      <c r="M31" s="13">
-        <f t="shared" si="7"/>
+      <c r="O31" s="13">
+        <f>G14*$Q$19</f>
         <v>85.724999999999994</v>
       </c>
-      <c r="N31" s="14">
-        <f t="shared" si="8"/>
+      <c r="P31" s="21">
+        <f t="shared" si="5"/>
+        <v>8.5724999999999998</v>
+      </c>
+      <c r="Q31" s="14">
+        <f>H14*$Q$19</f>
         <v>406.4</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B32" s="2" t="s">
         <v>17</v>
       </c>
@@ -1796,7 +1977,7 @@
         <v>5</v>
       </c>
       <c r="E32" s="17">
-        <f>D32*$M$19</f>
+        <f>D32*$Q$19</f>
         <v>127</v>
       </c>
       <c r="F32" s="17">
@@ -1804,40 +1985,52 @@
         <v>63.5</v>
       </c>
       <c r="G32" s="13">
+        <f>D15*$Q$19</f>
+        <v>6.5531999999999995</v>
+      </c>
+      <c r="H32" s="13">
+        <f>E15*$Q$19</f>
+        <v>9.5249999999999986</v>
+      </c>
+      <c r="I32" s="13">
         <f t="shared" si="1"/>
-        <v>6.5531999999999995</v>
-      </c>
-      <c r="H32" s="13">
+        <v>70.053200000000004</v>
+      </c>
+      <c r="J32" s="13">
         <f t="shared" si="2"/>
-        <v>9.5249999999999986</v>
-      </c>
-      <c r="I32" s="13">
-        <f t="shared" si="3"/>
-        <v>70.053200000000004</v>
-      </c>
-      <c r="J32" s="13">
-        <f t="shared" si="4"/>
         <v>73.025000000000006</v>
       </c>
       <c r="K32" s="13">
-        <f t="shared" si="5"/>
+        <f>F15*$Q$19</f>
         <v>141.30019999999999</v>
       </c>
       <c r="L32" s="13">
         <f t="shared" si="6"/>
+        <v>128.19379999999998</v>
+      </c>
+      <c r="M32" s="13">
+        <f t="shared" si="3"/>
+        <v>122.25019999999999</v>
+      </c>
+      <c r="N32" s="13">
+        <f t="shared" si="4"/>
         <v>70.650099999999995</v>
       </c>
-      <c r="M32" s="13">
-        <f t="shared" si="7"/>
+      <c r="O32" s="13">
+        <f>G15*$Q$19</f>
         <v>92.074999999999989</v>
       </c>
-      <c r="N32" s="14">
-        <f t="shared" si="8"/>
+      <c r="P32" s="21">
+        <f t="shared" si="5"/>
+        <v>9.2074999999999996</v>
+      </c>
+      <c r="Q32" s="14">
+        <f>H15*$Q$19</f>
         <v>609.59999999999991</v>
       </c>
-      <c r="P32"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="S32"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B33" s="2" t="s">
         <v>18</v>
       </c>
@@ -1848,7 +2041,7 @@
         <v>6</v>
       </c>
       <c r="E33" s="17">
-        <f>D33*$M$19</f>
+        <f>D33*$Q$19</f>
         <v>152.39999999999998</v>
       </c>
       <c r="F33" s="17">
@@ -1856,39 +2049,51 @@
         <v>76.199999999999989</v>
       </c>
       <c r="G33" s="13">
+        <f>D16*$Q$19</f>
+        <v>7.1120000000000001</v>
+      </c>
+      <c r="H33" s="13">
+        <f>E16*$Q$19</f>
+        <v>10.972799999999999</v>
+      </c>
+      <c r="I33" s="13">
         <f t="shared" si="1"/>
-        <v>7.1120000000000001</v>
-      </c>
-      <c r="H33" s="13">
+        <v>83.311999999999983</v>
+      </c>
+      <c r="J33" s="13">
         <f t="shared" si="2"/>
-        <v>10.972799999999999</v>
-      </c>
-      <c r="I33" s="13">
-        <f t="shared" si="3"/>
-        <v>83.311999999999983</v>
-      </c>
-      <c r="J33" s="13">
-        <f t="shared" si="4"/>
         <v>87.172799999999995</v>
       </c>
       <c r="K33" s="13">
-        <f t="shared" si="5"/>
+        <f>F16*$Q$19</f>
         <v>168.27499999999998</v>
       </c>
       <c r="L33" s="13">
         <f t="shared" si="6"/>
+        <v>154.05099999999999</v>
+      </c>
+      <c r="M33" s="13">
+        <f t="shared" si="3"/>
+        <v>146.32939999999996</v>
+      </c>
+      <c r="N33" s="13">
+        <f t="shared" si="4"/>
         <v>84.137499999999989</v>
       </c>
-      <c r="M33" s="13">
-        <f t="shared" si="7"/>
+      <c r="O33" s="13">
+        <f>G16*$Q$19</f>
         <v>95.25</v>
       </c>
-      <c r="N33" s="14">
-        <f t="shared" si="8"/>
+      <c r="P33" s="21">
+        <f t="shared" si="5"/>
+        <v>9.5250000000000004</v>
+      </c>
+      <c r="Q33" s="14">
+        <f>H16*$Q$19</f>
         <v>762</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B34" s="3" t="s">
         <v>17</v>
       </c>
@@ -1899,7 +2104,7 @@
         <v>8</v>
       </c>
       <c r="E34" s="18">
-        <f>D34*$M$19</f>
+        <f>D34*$Q$19</f>
         <v>203.2</v>
       </c>
       <c r="F34" s="18">
@@ -1907,52 +2112,67 @@
         <v>101.6</v>
       </c>
       <c r="G34" s="15">
+        <f>D17*$Q$19</f>
+        <v>8.178799999999999</v>
+      </c>
+      <c r="H34" s="15">
+        <f>E17*$Q$19</f>
+        <v>12.7</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="1"/>
-        <v>8.178799999999999</v>
-      </c>
-      <c r="H34" s="15">
+        <v>109.77879999999999</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="2"/>
-        <v>12.7</v>
-      </c>
-      <c r="I34" s="15">
+        <v>114.3</v>
+      </c>
+      <c r="K34" s="15">
+        <f>F17*$Q$19</f>
+        <v>219.07499999999999</v>
+      </c>
+      <c r="L34" s="13">
+        <f t="shared" si="6"/>
+        <v>202.7174</v>
+      </c>
+      <c r="M34" s="13">
         <f t="shared" si="3"/>
-        <v>109.77879999999999</v>
-      </c>
-      <c r="J34" s="15">
+        <v>193.67499999999998</v>
+      </c>
+      <c r="N34" s="15">
         <f t="shared" si="4"/>
-        <v>114.3</v>
-      </c>
-      <c r="K34" s="15">
+        <v>109.53749999999999</v>
+      </c>
+      <c r="O34" s="15">
+        <f>G17*$Q$19</f>
+        <v>165.1</v>
+      </c>
+      <c r="P34" s="22">
         <f t="shared" si="5"/>
-        <v>219.07499999999999</v>
-      </c>
-      <c r="L34" s="15">
-        <f t="shared" si="6"/>
-        <v>109.53749999999999</v>
-      </c>
-      <c r="M34" s="15">
-        <f t="shared" si="7"/>
-        <v>165.1</v>
-      </c>
-      <c r="N34" s="16">
-        <f t="shared" si="8"/>
+        <v>16.510000000000002</v>
+      </c>
+      <c r="Q34" s="16">
+        <f>H17*$Q$19</f>
         <v>901.69999999999993</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="20">
+    <mergeCell ref="M20:M21"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="K20:K21"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="Q20:Q21"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="F20:F21"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="P20:P21"/>
     <mergeCell ref="L20:L21"/>
-    <mergeCell ref="I20:J20"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
@@ -1960,6 +2180,10 @@
     <mergeCell ref="G3:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C7 C14:C17 C24 C32:C34" numberStoredAsText="1"/>
+    <ignoredError sqref="C8:C13 C25:C31" twoDigitTextYear="1" numberStoredAsText="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/file/table/DAPC_ElectricElbowBellEnd.xlsx
+++ b/file/table/DAPC_ElectricElbowBellEnd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E884C7A0-7683-4BDD-B3F8-460DFDEED6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8140813A-EBCC-461D-9376-50E02F72B59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D413FB54-6771-4A8E-8770-B93D70107D30}"/>
   </bookViews>
@@ -146,10 +146,10 @@
     <t>B' (mm) Min.</t>
   </si>
   <si>
-    <t>A' Sch40 (mm)</t>
-  </si>
-  <si>
-    <t>A' Sch80 (mm)</t>
+    <t>A'/2 Sch40 (mm)</t>
+  </si>
+  <si>
+    <t>A'/2 Sch80 (mm)</t>
   </si>
 </sst>
 </file>
@@ -490,22 +490,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>111369</xdr:colOff>
+      <xdr:colOff>78748</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>29306</xdr:rowOff>
+      <xdr:rowOff>52551</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>125509</xdr:colOff>
+      <xdr:colOff>185376</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>199293</xdr:rowOff>
+      <xdr:rowOff>210207</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE8C3A7D-1C76-D99C-0911-3C7361AE9139}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12C6A3F4-57C3-C593-2E34-B19392601FF2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -533,8 +533,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6183923" y="451337"/>
-          <a:ext cx="3596304" cy="3124202"/>
+          <a:off x="5460045" y="483475"/>
+          <a:ext cx="3680145" cy="3174125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1370,12 +1370,12 @@
         <v>21.335999999999999</v>
       </c>
       <c r="L22" s="13">
-        <f>$K22-2*G22</f>
-        <v>15.7988</v>
+        <f>($K22-2*G22)/2</f>
+        <v>7.8994</v>
       </c>
       <c r="M22" s="13">
-        <f>$K22-2*H22</f>
-        <v>13.868399999999999</v>
+        <f>($K22-2*H22)/2</f>
+        <v>6.9341999999999997</v>
       </c>
       <c r="N22" s="13">
         <f>K22/2</f>
@@ -1434,12 +1434,12 @@
         <v>26.669999999999998</v>
       </c>
       <c r="L23" s="13">
-        <f>K23-2*G23</f>
-        <v>20.929599999999997</v>
+        <f t="shared" ref="L23:M34" si="3">($K23-2*G23)/2</f>
+        <v>10.464799999999999</v>
       </c>
       <c r="M23" s="13">
-        <f t="shared" ref="M23:M34" si="3">$K23-2*H23</f>
-        <v>18.846799999999998</v>
+        <f t="shared" si="3"/>
+        <v>9.4233999999999991</v>
       </c>
       <c r="N23" s="13">
         <f t="shared" ref="N23:N34" si="4">K23/2</f>
@@ -1497,12 +1497,12 @@
         <v>33.400999999999996</v>
       </c>
       <c r="L24" s="13">
-        <f>K24-2*G24</f>
-        <v>26.644599999999997</v>
+        <f t="shared" si="3"/>
+        <v>13.322299999999998</v>
       </c>
       <c r="M24" s="13">
         <f t="shared" si="3"/>
-        <v>24.307799999999997</v>
+        <v>12.153899999999998</v>
       </c>
       <c r="N24" s="13">
         <f t="shared" si="4"/>
@@ -1561,12 +1561,12 @@
         <v>42.163999999999994</v>
       </c>
       <c r="L25" s="13">
-        <f>K25-2*G25</f>
-        <v>35.051999999999992</v>
+        <f t="shared" si="3"/>
+        <v>17.525999999999996</v>
       </c>
       <c r="M25" s="13">
         <f t="shared" si="3"/>
-        <v>32.461199999999991</v>
+        <v>16.230599999999995</v>
       </c>
       <c r="N25" s="13">
         <f t="shared" si="4"/>
@@ -1625,12 +1625,12 @@
         <v>48.26</v>
       </c>
       <c r="L26" s="13">
-        <f t="shared" ref="L26:L34" si="6">K26-2*G26</f>
-        <v>40.893999999999998</v>
+        <f t="shared" si="3"/>
+        <v>20.446999999999999</v>
       </c>
       <c r="M26" s="13">
         <f t="shared" si="3"/>
-        <v>38.099999999999994</v>
+        <v>19.049999999999997</v>
       </c>
       <c r="N26" s="13">
         <f t="shared" si="4"/>
@@ -1688,12 +1688,12 @@
         <v>60.324999999999996</v>
       </c>
       <c r="L27" s="13">
-        <f t="shared" si="6"/>
-        <v>52.501799999999996</v>
+        <f t="shared" si="3"/>
+        <v>26.250899999999998</v>
       </c>
       <c r="M27" s="13">
         <f t="shared" si="3"/>
-        <v>49.250599999999999</v>
+        <v>24.625299999999999</v>
       </c>
       <c r="N27" s="13">
         <f t="shared" si="4"/>
@@ -1752,12 +1752,12 @@
         <v>73.024999999999991</v>
       </c>
       <c r="L28" s="13">
-        <f t="shared" si="6"/>
-        <v>62.712599999999995</v>
+        <f t="shared" si="3"/>
+        <v>31.356299999999997</v>
       </c>
       <c r="M28" s="13">
         <f t="shared" si="3"/>
-        <v>59.00419999999999</v>
+        <v>29.502099999999995</v>
       </c>
       <c r="N28" s="13">
         <f t="shared" si="4"/>
@@ -1815,12 +1815,12 @@
         <v>88.899999999999991</v>
       </c>
       <c r="L29" s="13">
-        <f t="shared" si="6"/>
-        <v>77.927199999999999</v>
+        <f t="shared" si="3"/>
+        <v>38.9636</v>
       </c>
       <c r="M29" s="13">
         <f t="shared" si="3"/>
-        <v>73.66</v>
+        <v>36.83</v>
       </c>
       <c r="N29" s="13">
         <f t="shared" si="4"/>
@@ -1879,12 +1879,12 @@
         <v>101.6</v>
       </c>
       <c r="L30" s="13">
-        <f t="shared" si="6"/>
-        <v>90.119199999999992</v>
+        <f t="shared" si="3"/>
+        <v>45.059599999999996</v>
       </c>
       <c r="M30" s="13">
         <f t="shared" si="3"/>
-        <v>85.445599999999999</v>
+        <v>42.722799999999999</v>
       </c>
       <c r="N30" s="13">
         <f t="shared" si="4"/>
@@ -1942,12 +1942,12 @@
         <v>114.3</v>
       </c>
       <c r="L31" s="13">
-        <f t="shared" si="6"/>
-        <v>102.2604</v>
+        <f t="shared" si="3"/>
+        <v>51.130200000000002</v>
       </c>
       <c r="M31" s="13">
         <f t="shared" si="3"/>
-        <v>97.180399999999992</v>
+        <v>48.590199999999996</v>
       </c>
       <c r="N31" s="13">
         <f t="shared" si="4"/>
@@ -2005,12 +2005,12 @@
         <v>141.30019999999999</v>
       </c>
       <c r="L32" s="13">
-        <f t="shared" si="6"/>
-        <v>128.19379999999998</v>
+        <f t="shared" si="3"/>
+        <v>64.096899999999991</v>
       </c>
       <c r="M32" s="13">
         <f t="shared" si="3"/>
-        <v>122.25019999999999</v>
+        <v>61.125099999999996</v>
       </c>
       <c r="N32" s="13">
         <f t="shared" si="4"/>
@@ -2069,12 +2069,12 @@
         <v>168.27499999999998</v>
       </c>
       <c r="L33" s="13">
-        <f t="shared" si="6"/>
-        <v>154.05099999999999</v>
+        <f t="shared" si="3"/>
+        <v>77.025499999999994</v>
       </c>
       <c r="M33" s="13">
         <f t="shared" si="3"/>
-        <v>146.32939999999996</v>
+        <v>73.164699999999982</v>
       </c>
       <c r="N33" s="13">
         <f t="shared" si="4"/>
@@ -2131,13 +2131,13 @@
         <f>F17*$Q$19</f>
         <v>219.07499999999999</v>
       </c>
-      <c r="L34" s="13">
-        <f t="shared" si="6"/>
-        <v>202.7174</v>
-      </c>
-      <c r="M34" s="13">
-        <f t="shared" si="3"/>
-        <v>193.67499999999998</v>
+      <c r="L34" s="15">
+        <f t="shared" si="3"/>
+        <v>101.3587</v>
+      </c>
+      <c r="M34" s="15">
+        <f t="shared" si="3"/>
+        <v>96.837499999999991</v>
       </c>
       <c r="N34" s="15">
         <f t="shared" si="4"/>

--- a/file/table/DAPC_ElectricElbowBellEnd.xlsx
+++ b/file/table/DAPC_ElectricElbowBellEnd.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8140813A-EBCC-461D-9376-50E02F72B59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CFDD08-0A05-45F6-A143-D69538F30DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D413FB54-6771-4A8E-8770-B93D70107D30}"/>
   </bookViews>
   <sheets>
     <sheet name="ElectricElbowBellEnd" sheetId="1" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
   <si>
     <t>Item</t>
   </si>
@@ -104,12 +105,6 @@
     <t>A (in) Average</t>
   </si>
   <si>
-    <t>Sch40 &amp; Sch80 Standar Electric Elbow - Bell End (in)</t>
-  </si>
-  <si>
-    <t>Sch40 &amp; Sch80 Standar Electric Elbow - Bell End (mm)</t>
-  </si>
-  <si>
     <t>in to mm:</t>
   </si>
   <si>
@@ -150,13 +145,31 @@
   </si>
   <si>
     <t>A'/2 Sch80 (mm)</t>
+  </si>
+  <si>
+    <t>Metadata</t>
+  </si>
+  <si>
+    <t>LEDES / Sch40 &amp; Sch80 Standar Electric Elbow - Bell End (in)</t>
+  </si>
+  <si>
+    <t>LEDES / Sch40 &amp; Sch80 Standar Electric Elbow - Bell End (mm)</t>
+  </si>
+  <si>
+    <t>https://www.ledestube.com/es_mx/una-guia-completa-sobre-codos-para-conductos-electricos/</t>
+  </si>
+  <si>
+    <t>v.20250713</t>
+  </si>
+  <si>
+    <t>Pass: 1234</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +180,26 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -355,30 +388,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -386,9 +405,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -402,16 +418,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -420,8 +430,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -535,6 +569,56 @@
         <a:xfrm>
           <a:off x="5460045" y="483475"/>
           <a:ext cx="3680145" cy="3174125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>273538</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>156309</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>635997</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>181789</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F4184EA-EFB0-4419-A61D-A0F2B616BB65}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4370102" y="156309"/>
+          <a:ext cx="1000716" cy="240403"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -863,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03377F46-21A8-46AD-BDC5-1FB7BCB4429A}">
-  <dimension ref="B2:S34"/>
+  <dimension ref="B1:S34"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
@@ -884,65 +968,70 @@
     <col min="19" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H1" s="23" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="15"/>
+      <c r="F3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="12" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="18"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="7">
         <v>0.109</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="7">
         <v>0.14699999999999999</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="7">
         <v>0.84</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="7">
         <v>1.5</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="8">
         <v>4</v>
       </c>
     </row>
@@ -950,447 +1039,447 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="7">
         <v>0.113</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="7">
         <v>0.154</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="7">
         <v>1.05</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="7">
         <v>1.5</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="8">
         <v>4.5</v>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="7">
         <v>0.13300000000000001</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="7">
         <v>0.17899999999999999</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="7">
         <v>1.3149999999999999</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="7">
         <v>1.875</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="8">
         <v>5.75</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="7">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="7">
         <v>0.191</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="7">
         <v>1.66</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="7">
         <v>2</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="8">
         <v>7.25</v>
       </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="7">
         <v>0.14499999999999999</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="7">
         <v>0.2</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="7">
         <v>1.9</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="7">
         <v>2</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="8">
         <v>8.25</v>
       </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="7">
         <v>0.154</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="7">
         <v>0.218</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="7">
         <v>2.375</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="7">
         <v>2</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="8">
         <v>9.5</v>
       </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="7">
         <v>0.20300000000000001</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="7">
         <v>0.27600000000000002</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="7">
         <v>2.875</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="7">
         <v>3</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="8">
         <v>10.5</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="7">
         <v>0.216</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="7">
         <v>0.3</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="7">
         <v>3.5</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="7">
         <v>3.125</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="8">
         <v>13</v>
       </c>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="7">
         <v>0.22600000000000001</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="7">
         <v>0.318</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="7">
         <v>4</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="7">
         <v>3.25</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="8">
         <v>15</v>
       </c>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="7">
         <v>0.23699999999999999</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="7">
         <v>0.33700000000000002</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="7">
         <v>4.5</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="7">
         <v>3.375</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="8">
         <v>16</v>
       </c>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="7">
         <v>0.25800000000000001</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="7">
         <v>0.375</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="7">
         <v>5.5629999999999997</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="7">
         <v>3.625</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="8">
         <v>24</v>
       </c>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="7">
         <v>0.432</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="7">
         <v>6.625</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="7">
         <v>3.75</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="8">
         <v>30</v>
       </c>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="9">
         <v>0.32200000000000001</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="9">
         <v>0.5</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="9">
         <v>8.625</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="9">
         <v>6.5</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="10">
         <v>35.5</v>
       </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N19" s="11"/>
+      <c r="P19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B20" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="N19" s="19"/>
-      <c r="P19" s="19" t="s">
+      <c r="H20" s="15"/>
+      <c r="I20" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="Q19" s="19">
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B20" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="L20" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="N20" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="O20" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5" t="s">
+      <c r="P20" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q20" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="L20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="N20" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="21" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="7"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="12" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="9"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="18"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="7">
         <f>1/2</f>
         <v>0.5</v>
       </c>
-      <c r="E22" s="17">
-        <f>D22*$Q$19</f>
+      <c r="E22" s="7">
+        <f t="shared" ref="E22:E34" si="0">D22*$Q$19</f>
         <v>12.7</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="7">
         <f>E22/2</f>
         <v>6.35</v>
       </c>
-      <c r="G22" s="13">
-        <f>D5*$Q$19</f>
+      <c r="G22" s="7">
+        <f t="shared" ref="G22:G34" si="1">D5*$Q$19</f>
         <v>2.7685999999999997</v>
       </c>
-      <c r="H22" s="13">
-        <f>E5*$Q$19</f>
+      <c r="H22" s="7">
+        <f t="shared" ref="H22:H34" si="2">E5*$Q$19</f>
         <v>3.7337999999999996</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="7">
         <f>$F22+G22</f>
         <v>9.1185999999999989</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="7">
         <f>$F22+H22</f>
         <v>10.0838</v>
       </c>
-      <c r="K22" s="13">
-        <f>F5*$Q$19</f>
+      <c r="K22" s="7">
+        <f t="shared" ref="K22:K34" si="3">F5*$Q$19</f>
         <v>21.335999999999999</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="7">
         <f>($K22-2*G22)/2</f>
         <v>7.8994</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="7">
         <f>($K22-2*H22)/2</f>
         <v>6.9341999999999997</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="7">
         <f>K22/2</f>
         <v>10.667999999999999</v>
       </c>
-      <c r="O22" s="13">
-        <f>G5*$Q$19</f>
+      <c r="O22" s="7">
+        <f t="shared" ref="O22:O34" si="4">G5*$Q$19</f>
         <v>38.099999999999994</v>
       </c>
-      <c r="P22" s="21">
+      <c r="P22" s="13">
         <f>O22*0.1</f>
         <v>3.8099999999999996</v>
       </c>
-      <c r="Q22" s="14">
-        <f>H5*$Q$19</f>
+      <c r="Q22" s="8">
+        <f t="shared" ref="Q22:Q34" si="5">H5*$Q$19</f>
         <v>101.6</v>
       </c>
     </row>
@@ -1398,63 +1487,63 @@
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="7">
         <f>3/4</f>
         <v>0.75</v>
       </c>
-      <c r="E23" s="17">
-        <f>D23*$Q$19</f>
+      <c r="E23" s="7">
+        <f t="shared" si="0"/>
         <v>19.049999999999997</v>
       </c>
-      <c r="F23" s="17">
-        <f t="shared" ref="F23:F34" si="0">E23/2</f>
+      <c r="F23" s="7">
+        <f t="shared" ref="F23:F34" si="6">E23/2</f>
         <v>9.5249999999999986</v>
       </c>
-      <c r="G23" s="13">
-        <f>D6*$Q$19</f>
+      <c r="G23" s="7">
+        <f t="shared" si="1"/>
         <v>2.8702000000000001</v>
       </c>
-      <c r="H23" s="13">
-        <f>E6*$Q$19</f>
+      <c r="H23" s="7">
+        <f t="shared" si="2"/>
         <v>3.9115999999999995</v>
       </c>
-      <c r="I23" s="13">
-        <f t="shared" ref="I23:I34" si="1">$F23+G23</f>
+      <c r="I23" s="7">
+        <f t="shared" ref="I23:I34" si="7">$F23+G23</f>
         <v>12.395199999999999</v>
       </c>
-      <c r="J23" s="13">
-        <f t="shared" ref="J23:J34" si="2">$F23+H23</f>
+      <c r="J23" s="7">
+        <f t="shared" ref="J23:J34" si="8">$F23+H23</f>
         <v>13.436599999999999</v>
       </c>
-      <c r="K23" s="13">
-        <f>F6*$Q$19</f>
+      <c r="K23" s="7">
+        <f t="shared" si="3"/>
         <v>26.669999999999998</v>
       </c>
-      <c r="L23" s="13">
-        <f t="shared" ref="L23:M34" si="3">($K23-2*G23)/2</f>
+      <c r="L23" s="7">
+        <f t="shared" ref="L23:M34" si="9">($K23-2*G23)/2</f>
         <v>10.464799999999999</v>
       </c>
-      <c r="M23" s="13">
-        <f t="shared" si="3"/>
+      <c r="M23" s="7">
+        <f t="shared" si="9"/>
         <v>9.4233999999999991</v>
       </c>
-      <c r="N23" s="13">
-        <f t="shared" ref="N23:N34" si="4">K23/2</f>
+      <c r="N23" s="7">
+        <f t="shared" ref="N23:N34" si="10">K23/2</f>
         <v>13.334999999999999</v>
       </c>
-      <c r="O23" s="13">
-        <f>G6*$Q$19</f>
+      <c r="O23" s="7">
+        <f t="shared" si="4"/>
         <v>38.099999999999994</v>
       </c>
-      <c r="P23" s="21">
-        <f t="shared" ref="P23:P34" si="5">O23*0.1</f>
+      <c r="P23" s="13">
+        <f t="shared" ref="P23:P34" si="11">O23*0.1</f>
         <v>3.8099999999999996</v>
       </c>
-      <c r="Q23" s="14">
-        <f>H6*$Q$19</f>
+      <c r="Q23" s="8">
+        <f t="shared" si="5"/>
         <v>114.3</v>
       </c>
     </row>
@@ -1462,62 +1551,62 @@
       <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="7">
         <v>1</v>
       </c>
-      <c r="E24" s="17">
-        <f>D24*$Q$19</f>
+      <c r="E24" s="7">
+        <f t="shared" si="0"/>
         <v>25.4</v>
       </c>
-      <c r="F24" s="17">
-        <f t="shared" si="0"/>
+      <c r="F24" s="7">
+        <f t="shared" si="6"/>
         <v>12.7</v>
       </c>
-      <c r="G24" s="13">
-        <f>D7*$Q$19</f>
+      <c r="G24" s="7">
+        <f t="shared" si="1"/>
         <v>3.3782000000000001</v>
       </c>
-      <c r="H24" s="13">
-        <f>E7*$Q$19</f>
+      <c r="H24" s="7">
+        <f t="shared" si="2"/>
         <v>4.5465999999999998</v>
       </c>
-      <c r="I24" s="13">
-        <f t="shared" si="1"/>
+      <c r="I24" s="7">
+        <f t="shared" si="7"/>
         <v>16.078199999999999</v>
       </c>
-      <c r="J24" s="13">
-        <f t="shared" si="2"/>
+      <c r="J24" s="7">
+        <f t="shared" si="8"/>
         <v>17.246600000000001</v>
       </c>
-      <c r="K24" s="13">
-        <f>F7*$Q$19</f>
+      <c r="K24" s="7">
+        <f t="shared" si="3"/>
         <v>33.400999999999996</v>
       </c>
-      <c r="L24" s="13">
-        <f t="shared" si="3"/>
+      <c r="L24" s="7">
+        <f t="shared" si="9"/>
         <v>13.322299999999998</v>
       </c>
-      <c r="M24" s="13">
-        <f t="shared" si="3"/>
+      <c r="M24" s="7">
+        <f t="shared" si="9"/>
         <v>12.153899999999998</v>
       </c>
-      <c r="N24" s="13">
+      <c r="N24" s="7">
+        <f t="shared" si="10"/>
+        <v>16.700499999999998</v>
+      </c>
+      <c r="O24" s="7">
         <f t="shared" si="4"/>
-        <v>16.700499999999998</v>
-      </c>
-      <c r="O24" s="13">
-        <f>G7*$Q$19</f>
         <v>47.625</v>
       </c>
-      <c r="P24" s="21">
+      <c r="P24" s="13">
+        <f t="shared" si="11"/>
+        <v>4.7625000000000002</v>
+      </c>
+      <c r="Q24" s="8">
         <f t="shared" si="5"/>
-        <v>4.7625000000000002</v>
-      </c>
-      <c r="Q24" s="14">
-        <f>H7*$Q$19</f>
         <v>146.04999999999998</v>
       </c>
     </row>
@@ -1525,63 +1614,63 @@
       <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="7">
         <f>1+1/4</f>
         <v>1.25</v>
       </c>
-      <c r="E25" s="17">
-        <f>D25*$Q$19</f>
+      <c r="E25" s="7">
+        <f t="shared" si="0"/>
         <v>31.75</v>
       </c>
-      <c r="F25" s="17">
-        <f t="shared" si="0"/>
+      <c r="F25" s="7">
+        <f t="shared" si="6"/>
         <v>15.875</v>
       </c>
-      <c r="G25" s="13">
-        <f>D8*$Q$19</f>
+      <c r="G25" s="7">
+        <f t="shared" si="1"/>
         <v>3.556</v>
       </c>
-      <c r="H25" s="13">
-        <f>E8*$Q$19</f>
+      <c r="H25" s="7">
+        <f t="shared" si="2"/>
         <v>4.8513999999999999</v>
       </c>
-      <c r="I25" s="13">
-        <f t="shared" si="1"/>
+      <c r="I25" s="7">
+        <f t="shared" si="7"/>
         <v>19.431000000000001</v>
       </c>
-      <c r="J25" s="13">
-        <f t="shared" si="2"/>
+      <c r="J25" s="7">
+        <f t="shared" si="8"/>
         <v>20.726399999999998</v>
       </c>
-      <c r="K25" s="13">
-        <f>F8*$Q$19</f>
+      <c r="K25" s="7">
+        <f t="shared" si="3"/>
         <v>42.163999999999994</v>
       </c>
-      <c r="L25" s="13">
-        <f t="shared" si="3"/>
+      <c r="L25" s="7">
+        <f t="shared" si="9"/>
         <v>17.525999999999996</v>
       </c>
-      <c r="M25" s="13">
-        <f t="shared" si="3"/>
+      <c r="M25" s="7">
+        <f t="shared" si="9"/>
         <v>16.230599999999995</v>
       </c>
-      <c r="N25" s="13">
+      <c r="N25" s="7">
+        <f t="shared" si="10"/>
+        <v>21.081999999999997</v>
+      </c>
+      <c r="O25" s="7">
         <f t="shared" si="4"/>
-        <v>21.081999999999997</v>
-      </c>
-      <c r="O25" s="13">
-        <f>G8*$Q$19</f>
         <v>50.8</v>
       </c>
-      <c r="P25" s="21">
+      <c r="P25" s="13">
+        <f t="shared" si="11"/>
+        <v>5.08</v>
+      </c>
+      <c r="Q25" s="8">
         <f t="shared" si="5"/>
-        <v>5.08</v>
-      </c>
-      <c r="Q25" s="14">
-        <f>H8*$Q$19</f>
         <v>184.14999999999998</v>
       </c>
     </row>
@@ -1589,63 +1678,63 @@
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="7">
         <f>1+1/2</f>
         <v>1.5</v>
       </c>
-      <c r="E26" s="17">
-        <f>D26*$Q$19</f>
+      <c r="E26" s="7">
+        <f t="shared" si="0"/>
         <v>38.099999999999994</v>
       </c>
-      <c r="F26" s="17">
-        <f t="shared" si="0"/>
+      <c r="F26" s="7">
+        <f t="shared" si="6"/>
         <v>19.049999999999997</v>
       </c>
-      <c r="G26" s="13">
-        <f>D9*$Q$19</f>
+      <c r="G26" s="7">
+        <f t="shared" si="1"/>
         <v>3.6829999999999994</v>
       </c>
-      <c r="H26" s="13">
-        <f>E9*$Q$19</f>
+      <c r="H26" s="7">
+        <f t="shared" si="2"/>
         <v>5.08</v>
       </c>
-      <c r="I26" s="13">
-        <f t="shared" si="1"/>
+      <c r="I26" s="7">
+        <f t="shared" si="7"/>
         <v>22.732999999999997</v>
       </c>
-      <c r="J26" s="13">
-        <f t="shared" si="2"/>
+      <c r="J26" s="7">
+        <f t="shared" si="8"/>
         <v>24.129999999999995</v>
       </c>
-      <c r="K26" s="13">
-        <f>F9*$Q$19</f>
+      <c r="K26" s="7">
+        <f t="shared" si="3"/>
         <v>48.26</v>
       </c>
-      <c r="L26" s="13">
-        <f t="shared" si="3"/>
+      <c r="L26" s="7">
+        <f t="shared" si="9"/>
         <v>20.446999999999999</v>
       </c>
-      <c r="M26" s="13">
-        <f t="shared" si="3"/>
+      <c r="M26" s="7">
+        <f t="shared" si="9"/>
         <v>19.049999999999997</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="7">
+        <f t="shared" si="10"/>
+        <v>24.13</v>
+      </c>
+      <c r="O26" s="7">
         <f t="shared" si="4"/>
-        <v>24.13</v>
-      </c>
-      <c r="O26" s="13">
-        <f>G9*$Q$19</f>
         <v>50.8</v>
       </c>
-      <c r="P26" s="21">
+      <c r="P26" s="13">
+        <f t="shared" si="11"/>
+        <v>5.08</v>
+      </c>
+      <c r="Q26" s="8">
         <f t="shared" si="5"/>
-        <v>5.08</v>
-      </c>
-      <c r="Q26" s="14">
-        <f>H9*$Q$19</f>
         <v>209.54999999999998</v>
       </c>
     </row>
@@ -1653,62 +1742,62 @@
       <c r="B27" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="7">
         <v>2</v>
       </c>
-      <c r="E27" s="17">
-        <f>D27*$Q$19</f>
+      <c r="E27" s="7">
+        <f t="shared" si="0"/>
         <v>50.8</v>
       </c>
-      <c r="F27" s="17">
-        <f t="shared" si="0"/>
+      <c r="F27" s="7">
+        <f t="shared" si="6"/>
         <v>25.4</v>
       </c>
-      <c r="G27" s="13">
-        <f>D10*$Q$19</f>
+      <c r="G27" s="7">
+        <f t="shared" si="1"/>
         <v>3.9115999999999995</v>
       </c>
-      <c r="H27" s="13">
-        <f>E10*$Q$19</f>
+      <c r="H27" s="7">
+        <f t="shared" si="2"/>
         <v>5.5371999999999995</v>
       </c>
-      <c r="I27" s="13">
-        <f t="shared" si="1"/>
+      <c r="I27" s="7">
+        <f t="shared" si="7"/>
         <v>29.311599999999999</v>
       </c>
-      <c r="J27" s="13">
-        <f t="shared" si="2"/>
+      <c r="J27" s="7">
+        <f t="shared" si="8"/>
         <v>30.937199999999997</v>
       </c>
-      <c r="K27" s="13">
-        <f>F10*$Q$19</f>
+      <c r="K27" s="7">
+        <f t="shared" si="3"/>
         <v>60.324999999999996</v>
       </c>
-      <c r="L27" s="13">
-        <f t="shared" si="3"/>
+      <c r="L27" s="7">
+        <f t="shared" si="9"/>
         <v>26.250899999999998</v>
       </c>
-      <c r="M27" s="13">
-        <f t="shared" si="3"/>
+      <c r="M27" s="7">
+        <f t="shared" si="9"/>
         <v>24.625299999999999</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="7">
+        <f t="shared" si="10"/>
+        <v>30.162499999999998</v>
+      </c>
+      <c r="O27" s="7">
         <f t="shared" si="4"/>
-        <v>30.162499999999998</v>
-      </c>
-      <c r="O27" s="13">
-        <f>G10*$Q$19</f>
         <v>50.8</v>
       </c>
-      <c r="P27" s="21">
+      <c r="P27" s="13">
+        <f t="shared" si="11"/>
+        <v>5.08</v>
+      </c>
+      <c r="Q27" s="8">
         <f t="shared" si="5"/>
-        <v>5.08</v>
-      </c>
-      <c r="Q27" s="14">
-        <f>H10*$Q$19</f>
         <v>241.29999999999998</v>
       </c>
     </row>
@@ -1716,63 +1805,63 @@
       <c r="B28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="7">
         <f>2+1/2</f>
         <v>2.5</v>
       </c>
-      <c r="E28" s="17">
-        <f>D28*$Q$19</f>
+      <c r="E28" s="7">
+        <f t="shared" si="0"/>
         <v>63.5</v>
       </c>
-      <c r="F28" s="17">
-        <f t="shared" si="0"/>
+      <c r="F28" s="7">
+        <f t="shared" si="6"/>
         <v>31.75</v>
       </c>
-      <c r="G28" s="13">
-        <f>D11*$Q$19</f>
+      <c r="G28" s="7">
+        <f t="shared" si="1"/>
         <v>5.1562000000000001</v>
       </c>
-      <c r="H28" s="13">
-        <f>E11*$Q$19</f>
+      <c r="H28" s="7">
+        <f t="shared" si="2"/>
         <v>7.0104000000000006</v>
       </c>
-      <c r="I28" s="13">
-        <f t="shared" si="1"/>
+      <c r="I28" s="7">
+        <f t="shared" si="7"/>
         <v>36.906199999999998</v>
       </c>
-      <c r="J28" s="13">
-        <f t="shared" si="2"/>
+      <c r="J28" s="7">
+        <f t="shared" si="8"/>
         <v>38.760400000000004</v>
       </c>
-      <c r="K28" s="13">
-        <f>F11*$Q$19</f>
+      <c r="K28" s="7">
+        <f t="shared" si="3"/>
         <v>73.024999999999991</v>
       </c>
-      <c r="L28" s="13">
-        <f t="shared" si="3"/>
+      <c r="L28" s="7">
+        <f t="shared" si="9"/>
         <v>31.356299999999997</v>
       </c>
-      <c r="M28" s="13">
-        <f t="shared" si="3"/>
+      <c r="M28" s="7">
+        <f t="shared" si="9"/>
         <v>29.502099999999995</v>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="7">
+        <f t="shared" si="10"/>
+        <v>36.512499999999996</v>
+      </c>
+      <c r="O28" s="7">
         <f t="shared" si="4"/>
-        <v>36.512499999999996</v>
-      </c>
-      <c r="O28" s="13">
-        <f>G11*$Q$19</f>
         <v>76.199999999999989</v>
       </c>
-      <c r="P28" s="21">
+      <c r="P28" s="13">
+        <f t="shared" si="11"/>
+        <v>7.6199999999999992</v>
+      </c>
+      <c r="Q28" s="8">
         <f t="shared" si="5"/>
-        <v>7.6199999999999992</v>
-      </c>
-      <c r="Q28" s="14">
-        <f>H11*$Q$19</f>
         <v>266.7</v>
       </c>
     </row>
@@ -1780,62 +1869,62 @@
       <c r="B29" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="7">
         <v>3</v>
       </c>
-      <c r="E29" s="17">
-        <f>D29*$Q$19</f>
+      <c r="E29" s="7">
+        <f t="shared" si="0"/>
         <v>76.199999999999989</v>
       </c>
-      <c r="F29" s="17">
-        <f t="shared" si="0"/>
+      <c r="F29" s="7">
+        <f t="shared" si="6"/>
         <v>38.099999999999994</v>
       </c>
-      <c r="G29" s="13">
-        <f>D12*$Q$19</f>
+      <c r="G29" s="7">
+        <f t="shared" si="1"/>
         <v>5.4863999999999997</v>
       </c>
-      <c r="H29" s="13">
-        <f>E12*$Q$19</f>
+      <c r="H29" s="7">
+        <f t="shared" si="2"/>
         <v>7.6199999999999992</v>
       </c>
-      <c r="I29" s="13">
-        <f t="shared" si="1"/>
+      <c r="I29" s="7">
+        <f t="shared" si="7"/>
         <v>43.586399999999998</v>
       </c>
-      <c r="J29" s="13">
-        <f t="shared" si="2"/>
+      <c r="J29" s="7">
+        <f t="shared" si="8"/>
         <v>45.719999999999992</v>
       </c>
-      <c r="K29" s="13">
-        <f>F12*$Q$19</f>
+      <c r="K29" s="7">
+        <f t="shared" si="3"/>
         <v>88.899999999999991</v>
       </c>
-      <c r="L29" s="13">
-        <f t="shared" si="3"/>
+      <c r="L29" s="7">
+        <f t="shared" si="9"/>
         <v>38.9636</v>
       </c>
-      <c r="M29" s="13">
-        <f t="shared" si="3"/>
+      <c r="M29" s="7">
+        <f t="shared" si="9"/>
         <v>36.83</v>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="7">
+        <f t="shared" si="10"/>
+        <v>44.449999999999996</v>
+      </c>
+      <c r="O29" s="7">
         <f t="shared" si="4"/>
-        <v>44.449999999999996</v>
-      </c>
-      <c r="O29" s="13">
-        <f>G12*$Q$19</f>
         <v>79.375</v>
       </c>
-      <c r="P29" s="21">
+      <c r="P29" s="13">
+        <f t="shared" si="11"/>
+        <v>7.9375</v>
+      </c>
+      <c r="Q29" s="8">
         <f t="shared" si="5"/>
-        <v>7.9375</v>
-      </c>
-      <c r="Q29" s="14">
-        <f>H12*$Q$19</f>
         <v>330.2</v>
       </c>
     </row>
@@ -1843,63 +1932,63 @@
       <c r="B30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="7">
         <f>3+1/2</f>
         <v>3.5</v>
       </c>
-      <c r="E30" s="17">
-        <f>D30*$Q$19</f>
+      <c r="E30" s="7">
+        <f t="shared" si="0"/>
         <v>88.899999999999991</v>
       </c>
-      <c r="F30" s="17">
-        <f t="shared" si="0"/>
+      <c r="F30" s="7">
+        <f t="shared" si="6"/>
         <v>44.449999999999996</v>
       </c>
-      <c r="G30" s="13">
-        <f>D13*$Q$19</f>
+      <c r="G30" s="7">
+        <f t="shared" si="1"/>
         <v>5.7404000000000002</v>
       </c>
-      <c r="H30" s="13">
-        <f>E13*$Q$19</f>
+      <c r="H30" s="7">
+        <f t="shared" si="2"/>
         <v>8.0771999999999995</v>
       </c>
-      <c r="I30" s="13">
-        <f t="shared" si="1"/>
+      <c r="I30" s="7">
+        <f t="shared" si="7"/>
         <v>50.190399999999997</v>
       </c>
-      <c r="J30" s="13">
-        <f t="shared" si="2"/>
+      <c r="J30" s="7">
+        <f t="shared" si="8"/>
         <v>52.527199999999993</v>
       </c>
-      <c r="K30" s="13">
-        <f>F13*$Q$19</f>
+      <c r="K30" s="7">
+        <f t="shared" si="3"/>
         <v>101.6</v>
       </c>
-      <c r="L30" s="13">
-        <f t="shared" si="3"/>
+      <c r="L30" s="7">
+        <f t="shared" si="9"/>
         <v>45.059599999999996</v>
       </c>
-      <c r="M30" s="13">
-        <f t="shared" si="3"/>
+      <c r="M30" s="7">
+        <f t="shared" si="9"/>
         <v>42.722799999999999</v>
       </c>
-      <c r="N30" s="13">
+      <c r="N30" s="7">
+        <f t="shared" si="10"/>
+        <v>50.8</v>
+      </c>
+      <c r="O30" s="7">
         <f t="shared" si="4"/>
-        <v>50.8</v>
-      </c>
-      <c r="O30" s="13">
-        <f>G13*$Q$19</f>
         <v>82.55</v>
       </c>
-      <c r="P30" s="21">
+      <c r="P30" s="13">
+        <f t="shared" si="11"/>
+        <v>8.2550000000000008</v>
+      </c>
+      <c r="Q30" s="8">
         <f t="shared" si="5"/>
-        <v>8.2550000000000008</v>
-      </c>
-      <c r="Q30" s="14">
-        <f>H13*$Q$19</f>
         <v>381</v>
       </c>
     </row>
@@ -1907,62 +1996,62 @@
       <c r="B31" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="7">
         <v>4</v>
       </c>
-      <c r="E31" s="17">
-        <f>D31*$Q$19</f>
+      <c r="E31" s="7">
+        <f t="shared" si="0"/>
         <v>101.6</v>
       </c>
-      <c r="F31" s="17">
-        <f t="shared" si="0"/>
+      <c r="F31" s="7">
+        <f t="shared" si="6"/>
         <v>50.8</v>
       </c>
-      <c r="G31" s="13">
-        <f>D14*$Q$19</f>
+      <c r="G31" s="7">
+        <f t="shared" si="1"/>
         <v>6.0197999999999992</v>
       </c>
-      <c r="H31" s="13">
-        <f>E14*$Q$19</f>
+      <c r="H31" s="7">
+        <f t="shared" si="2"/>
         <v>8.5597999999999992</v>
       </c>
-      <c r="I31" s="13">
-        <f t="shared" si="1"/>
+      <c r="I31" s="7">
+        <f t="shared" si="7"/>
         <v>56.819799999999994</v>
       </c>
-      <c r="J31" s="13">
-        <f t="shared" si="2"/>
+      <c r="J31" s="7">
+        <f t="shared" si="8"/>
         <v>59.359799999999993</v>
       </c>
-      <c r="K31" s="13">
-        <f>F14*$Q$19</f>
+      <c r="K31" s="7">
+        <f t="shared" si="3"/>
         <v>114.3</v>
       </c>
-      <c r="L31" s="13">
-        <f t="shared" si="3"/>
+      <c r="L31" s="7">
+        <f t="shared" si="9"/>
         <v>51.130200000000002</v>
       </c>
-      <c r="M31" s="13">
-        <f t="shared" si="3"/>
+      <c r="M31" s="7">
+        <f t="shared" si="9"/>
         <v>48.590199999999996</v>
       </c>
-      <c r="N31" s="13">
+      <c r="N31" s="7">
+        <f t="shared" si="10"/>
+        <v>57.15</v>
+      </c>
+      <c r="O31" s="7">
         <f t="shared" si="4"/>
-        <v>57.15</v>
-      </c>
-      <c r="O31" s="13">
-        <f>G14*$Q$19</f>
         <v>85.724999999999994</v>
       </c>
-      <c r="P31" s="21">
+      <c r="P31" s="13">
+        <f t="shared" si="11"/>
+        <v>8.5724999999999998</v>
+      </c>
+      <c r="Q31" s="8">
         <f t="shared" si="5"/>
-        <v>8.5724999999999998</v>
-      </c>
-      <c r="Q31" s="14">
-        <f>H14*$Q$19</f>
         <v>406.4</v>
       </c>
     </row>
@@ -1970,62 +2059,62 @@
       <c r="B32" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="7">
         <v>5</v>
       </c>
-      <c r="E32" s="17">
-        <f>D32*$Q$19</f>
+      <c r="E32" s="7">
+        <f t="shared" si="0"/>
         <v>127</v>
       </c>
-      <c r="F32" s="17">
-        <f t="shared" si="0"/>
+      <c r="F32" s="7">
+        <f t="shared" si="6"/>
         <v>63.5</v>
       </c>
-      <c r="G32" s="13">
-        <f>D15*$Q$19</f>
+      <c r="G32" s="7">
+        <f t="shared" si="1"/>
         <v>6.5531999999999995</v>
       </c>
-      <c r="H32" s="13">
-        <f>E15*$Q$19</f>
+      <c r="H32" s="7">
+        <f t="shared" si="2"/>
         <v>9.5249999999999986</v>
       </c>
-      <c r="I32" s="13">
-        <f t="shared" si="1"/>
+      <c r="I32" s="7">
+        <f t="shared" si="7"/>
         <v>70.053200000000004</v>
       </c>
-      <c r="J32" s="13">
-        <f t="shared" si="2"/>
+      <c r="J32" s="7">
+        <f t="shared" si="8"/>
         <v>73.025000000000006</v>
       </c>
-      <c r="K32" s="13">
-        <f>F15*$Q$19</f>
+      <c r="K32" s="7">
+        <f t="shared" si="3"/>
         <v>141.30019999999999</v>
       </c>
-      <c r="L32" s="13">
-        <f t="shared" si="3"/>
+      <c r="L32" s="7">
+        <f t="shared" si="9"/>
         <v>64.096899999999991</v>
       </c>
-      <c r="M32" s="13">
-        <f t="shared" si="3"/>
+      <c r="M32" s="7">
+        <f t="shared" si="9"/>
         <v>61.125099999999996</v>
       </c>
-      <c r="N32" s="13">
+      <c r="N32" s="7">
+        <f t="shared" si="10"/>
+        <v>70.650099999999995</v>
+      </c>
+      <c r="O32" s="7">
         <f t="shared" si="4"/>
-        <v>70.650099999999995</v>
-      </c>
-      <c r="O32" s="13">
-        <f>G15*$Q$19</f>
         <v>92.074999999999989</v>
       </c>
-      <c r="P32" s="21">
+      <c r="P32" s="13">
+        <f t="shared" si="11"/>
+        <v>9.2074999999999996</v>
+      </c>
+      <c r="Q32" s="8">
         <f t="shared" si="5"/>
-        <v>9.2074999999999996</v>
-      </c>
-      <c r="Q32" s="14">
-        <f>H15*$Q$19</f>
         <v>609.59999999999991</v>
       </c>
       <c r="S32"/>
@@ -2034,62 +2123,62 @@
       <c r="B33" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="7">
         <v>6</v>
       </c>
-      <c r="E33" s="17">
-        <f>D33*$Q$19</f>
+      <c r="E33" s="7">
+        <f t="shared" si="0"/>
         <v>152.39999999999998</v>
       </c>
-      <c r="F33" s="17">
-        <f t="shared" si="0"/>
+      <c r="F33" s="7">
+        <f t="shared" si="6"/>
         <v>76.199999999999989</v>
       </c>
-      <c r="G33" s="13">
-        <f>D16*$Q$19</f>
+      <c r="G33" s="7">
+        <f t="shared" si="1"/>
         <v>7.1120000000000001</v>
       </c>
-      <c r="H33" s="13">
-        <f>E16*$Q$19</f>
+      <c r="H33" s="7">
+        <f t="shared" si="2"/>
         <v>10.972799999999999</v>
       </c>
-      <c r="I33" s="13">
-        <f t="shared" si="1"/>
+      <c r="I33" s="7">
+        <f t="shared" si="7"/>
         <v>83.311999999999983</v>
       </c>
-      <c r="J33" s="13">
-        <f t="shared" si="2"/>
+      <c r="J33" s="7">
+        <f t="shared" si="8"/>
         <v>87.172799999999995</v>
       </c>
-      <c r="K33" s="13">
-        <f>F16*$Q$19</f>
+      <c r="K33" s="7">
+        <f t="shared" si="3"/>
         <v>168.27499999999998</v>
       </c>
-      <c r="L33" s="13">
-        <f t="shared" si="3"/>
+      <c r="L33" s="7">
+        <f t="shared" si="9"/>
         <v>77.025499999999994</v>
       </c>
-      <c r="M33" s="13">
-        <f t="shared" si="3"/>
+      <c r="M33" s="7">
+        <f t="shared" si="9"/>
         <v>73.164699999999982</v>
       </c>
-      <c r="N33" s="13">
+      <c r="N33" s="7">
+        <f t="shared" si="10"/>
+        <v>84.137499999999989</v>
+      </c>
+      <c r="O33" s="7">
         <f t="shared" si="4"/>
-        <v>84.137499999999989</v>
-      </c>
-      <c r="O33" s="13">
-        <f>G16*$Q$19</f>
         <v>95.25</v>
       </c>
-      <c r="P33" s="21">
+      <c r="P33" s="13">
+        <f t="shared" si="11"/>
+        <v>9.5250000000000004</v>
+      </c>
+      <c r="Q33" s="8">
         <f t="shared" si="5"/>
-        <v>9.5250000000000004</v>
-      </c>
-      <c r="Q33" s="14">
-        <f>H16*$Q$19</f>
         <v>762</v>
       </c>
     </row>
@@ -2097,73 +2186,68 @@
       <c r="B34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="9">
         <v>8</v>
       </c>
-      <c r="E34" s="18">
-        <f>D34*$Q$19</f>
+      <c r="E34" s="9">
+        <f t="shared" si="0"/>
         <v>203.2</v>
       </c>
-      <c r="F34" s="18">
-        <f t="shared" si="0"/>
+      <c r="F34" s="9">
+        <f t="shared" si="6"/>
         <v>101.6</v>
       </c>
-      <c r="G34" s="15">
-        <f>D17*$Q$19</f>
+      <c r="G34" s="9">
+        <f t="shared" si="1"/>
         <v>8.178799999999999</v>
       </c>
-      <c r="H34" s="15">
-        <f>E17*$Q$19</f>
+      <c r="H34" s="9">
+        <f t="shared" si="2"/>
         <v>12.7</v>
       </c>
-      <c r="I34" s="15">
-        <f t="shared" si="1"/>
+      <c r="I34" s="9">
+        <f t="shared" si="7"/>
         <v>109.77879999999999</v>
       </c>
-      <c r="J34" s="15">
-        <f t="shared" si="2"/>
+      <c r="J34" s="9">
+        <f t="shared" si="8"/>
         <v>114.3</v>
       </c>
-      <c r="K34" s="15">
-        <f>F17*$Q$19</f>
+      <c r="K34" s="9">
+        <f t="shared" si="3"/>
         <v>219.07499999999999</v>
       </c>
-      <c r="L34" s="15">
-        <f t="shared" si="3"/>
+      <c r="L34" s="9">
+        <f t="shared" si="9"/>
         <v>101.3587</v>
       </c>
-      <c r="M34" s="15">
-        <f t="shared" si="3"/>
+      <c r="M34" s="9">
+        <f t="shared" si="9"/>
         <v>96.837499999999991</v>
       </c>
-      <c r="N34" s="15">
+      <c r="N34" s="9">
+        <f t="shared" si="10"/>
+        <v>109.53749999999999</v>
+      </c>
+      <c r="O34" s="9">
         <f t="shared" si="4"/>
-        <v>109.53749999999999</v>
-      </c>
-      <c r="O34" s="15">
-        <f>G17*$Q$19</f>
         <v>165.1</v>
       </c>
-      <c r="P34" s="22">
+      <c r="P34" s="14">
+        <f t="shared" si="11"/>
+        <v>16.510000000000002</v>
+      </c>
+      <c r="Q34" s="10">
         <f t="shared" si="5"/>
-        <v>16.510000000000002</v>
-      </c>
-      <c r="Q34" s="16">
-        <f>H17*$Q$19</f>
         <v>901.69999999999993</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="pzamqJiJJr/c/hifgHgAgxmarpqUpuWqMhM+n2GOV94iuiF1qYEyIFm5vX2byPAOT+Aewmkb1ffWCtFeCBYa+w==" saltValue="1Sn9oyki7cwVh5yYiY/qeA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="20">
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="K20:K21"/>
     <mergeCell ref="O20:O21"/>
     <mergeCell ref="Q20:Q21"/>
     <mergeCell ref="E20:E21"/>
@@ -2173,6 +2257,12 @@
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="P20:P21"/>
     <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="K20:K21"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
@@ -2186,4 +2276,37 @@
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C2A738-3364-4C23-96A1-AD55C940BA1E}">
+  <dimension ref="B2:B4"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="79.77734375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B3" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B4" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{AC1D5CB1-695E-4CE2-90FD-A746E9C65427}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/file/table/DAPC_ElectricElbowBellEnd.xlsx
+++ b/file/table/DAPC_ElectricElbowBellEnd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29309"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CFDD08-0A05-45F6-A143-D69538F30DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538206FF-2FB5-448E-9662-E36FA6EF419C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D413FB54-6771-4A8E-8770-B93D70107D30}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{D413FB54-6771-4A8E-8770-B93D70107D30}"/>
   </bookViews>
   <sheets>
     <sheet name="ElectricElbowBellEnd" sheetId="1" r:id="rId1"/>
@@ -108,18 +108,9 @@
     <t>in to mm:</t>
   </si>
   <si>
-    <t>Min. Wall (mm)</t>
-  </si>
-  <si>
     <t>A (mm) Average</t>
   </si>
   <si>
-    <t>B (mm) Min.</t>
-  </si>
-  <si>
-    <t>R (mm)</t>
-  </si>
-  <si>
     <t>Trade size Ø (in)</t>
   </si>
   <si>
@@ -129,21 +120,12 @@
     <t>Trade size Ø (in frac.)</t>
   </si>
   <si>
-    <t>Trade size Ø/2 (mm)</t>
-  </si>
-  <si>
     <t>A/2 (mm) Average</t>
   </si>
   <si>
     <t>External Wall offset (mm)</t>
   </si>
   <si>
-    <t>B' (mm) Min.</t>
-  </si>
-  <si>
-    <t>A'/2 Sch40 (mm)</t>
-  </si>
-  <si>
     <t>A'/2 Sch80 (mm)</t>
   </si>
   <si>
@@ -163,13 +145,139 @@
   </si>
   <si>
     <t>Pass: 1234</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>A'/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Sch40 (mm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>(mm) Min.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (mm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trade size</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Ø/2 (mm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>B'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (mm) Min.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Min. Wall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (mm)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +308,13 @@
     <font>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -430,6 +545,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -447,11 +567,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -531,8 +646,8 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>185376</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>210207</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2610</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -948,71 +1063,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03377F46-21A8-46AD-BDC5-1FB7BCB4429A}">
   <dimension ref="B1:S34"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.46484375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.86328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.46484375" style="1" customWidth="1"/>
     <col min="7" max="8" width="9.33203125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="11.88671875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5546875" style="1" customWidth="1"/>
-    <col min="12" max="13" width="9.88671875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="11.86328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.53125" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9.86328125" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.33203125" style="1" customWidth="1"/>
     <col min="15" max="15" width="9.33203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1328125" style="1" customWidth="1"/>
     <col min="17" max="17" width="8" style="1" customWidth="1"/>
     <col min="18" max="18" width="8.33203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="1"/>
+    <col min="19" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H1" s="23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.6">
+      <c r="H1" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B3" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.6">
+      <c r="B3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="C3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15" t="s">
+      <c r="E3" s="18"/>
+      <c r="F3" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="20"/>
-      <c r="C4" s="16"/>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.6">
+      <c r="B4" s="23"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="18"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="21"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1035,7 +1150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
@@ -1060,7 +1175,7 @@
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1085,7 +1200,7 @@
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
@@ -1110,7 +1225,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1135,7 +1250,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1160,7 +1275,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1185,7 +1300,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1210,7 +1325,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
@@ -1235,7 +1350,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
@@ -1260,7 +1375,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
@@ -1285,7 +1400,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.6">
       <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
@@ -1310,7 +1425,7 @@
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
@@ -1335,9 +1450,9 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N19" s="11"/>
       <c r="P19" s="11" t="s">
@@ -1347,58 +1462,58 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B20" s="19" t="s">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.6">
+      <c r="B20" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M20" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="M20" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="N20" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="O20" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="P20" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q20" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="20"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="O20" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q20" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B21" s="23"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="4" t="s">
         <v>1</v>
       </c>
@@ -1411,15 +1526,15 @@
       <c r="J21" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="18"/>
-    </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="21"/>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1483,7 +1598,7 @@
         <v>101.6</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
@@ -1547,7 +1662,7 @@
         <v>114.3</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
@@ -1610,7 +1725,7 @@
         <v>146.04999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
@@ -1674,7 +1789,7 @@
         <v>184.14999999999998</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
@@ -1738,7 +1853,7 @@
         <v>209.54999999999998</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B27" s="2" t="s">
         <v>18</v>
       </c>
@@ -1801,7 +1916,7 @@
         <v>241.29999999999998</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B28" s="2" t="s">
         <v>17</v>
       </c>
@@ -1865,7 +1980,7 @@
         <v>266.7</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B29" s="2" t="s">
         <v>18</v>
       </c>
@@ -1928,7 +2043,7 @@
         <v>330.2</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B30" s="2" t="s">
         <v>17</v>
       </c>
@@ -1992,7 +2107,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B31" s="2" t="s">
         <v>18</v>
       </c>
@@ -2055,7 +2170,7 @@
         <v>406.4</v>
       </c>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.6">
       <c r="B32" s="2" t="s">
         <v>17</v>
       </c>
@@ -2119,7 +2234,7 @@
       </c>
       <c r="S32"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.6">
       <c r="B33" s="2" t="s">
         <v>18</v>
       </c>
@@ -2182,7 +2297,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.6">
       <c r="B34" s="3" t="s">
         <v>17</v>
       </c>
@@ -2246,8 +2361,17 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pzamqJiJJr/c/hifgHgAgxmarpqUpuWqMhM+n2GOV94iuiF1qYEyIFm5vX2byPAOT+Aewmkb1ffWCtFeCBYa+w==" saltValue="1Sn9oyki7cwVh5yYiY/qeA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="20">
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
     <mergeCell ref="O20:O21"/>
     <mergeCell ref="Q20:Q21"/>
     <mergeCell ref="E20:E21"/>
@@ -2258,16 +2382,6 @@
     <mergeCell ref="P20:P21"/>
     <mergeCell ref="L20:L21"/>
     <mergeCell ref="M20:M21"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -2281,26 +2395,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C2A738-3364-4C23-96A1-AD55C940BA1E}">
   <dimension ref="B2:B4"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="79.77734375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="2.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="79.796875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" s="21" t="s">
-        <v>41</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.6">
+      <c r="B3" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.6">
+      <c r="B4" s="15" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
